--- a/data/trans_dic/IP12B$estomago-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$estomago-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por problemas de estómago o digestivos</t>
+          <t>Menores que han limitado su actividad por síntomas o dolor por problemas de estómago o digestivos (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,48</t>
+          <t>0,0; 20,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,86</t>
+          <t>0,0; 30,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,66</t>
+          <t>0,0; 51,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 5,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,27</t>
+          <t>0,0; 12,51</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,76</t>
+          <t>0,0; 32,22</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,05</t>
+          <t>0,0; 26,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 6,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,55</t>
+          <t>0,0; 16,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,47</t>
+          <t>0,0; 21,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,76</t>
+          <t>0,0; 27,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 7,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,77</t>
+          <t>0,0; 16,08</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,47</t>
+          <t>0,0; 11,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,54</t>
+          <t>0,0; 10,07</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,45</t>
+          <t>0,0; 23,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,76</t>
+          <t>0,0; 25,83</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,4</t>
+          <t>0,0; 17,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,62</t>
+          <t>0,0; 29,19</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,17</t>
+          <t>0,0; 13,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,37</t>
+          <t>0,0; 9,24</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,09; 21,57</t>
+          <t>2,1; 21,46</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 8,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 9,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,78</t>
+          <t>0,0; 38,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 6,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,06</t>
+          <t>0,0; 24,92</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0; 3,82</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0; 5,61</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 9,15</t>
+          <t>1,01; 9,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,79</t>
+          <t>0,0; 6,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 8,7</t>
+          <t>1,01; 9,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,38; 10,37</t>
+          <t>1,38; 11,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,05</t>
+          <t>0,0; 6,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,47; 14,57</t>
+          <t>1,46; 13,42</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,48; 8,42</t>
+          <t>1,48; 8,56</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,3</t>
+          <t>0,48; 4,68</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,48; 8,91</t>
+          <t>1,79; 9,16</t>
         </is>
       </c>
     </row>
@@ -1182,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han limitado su actividad por síntomas o dolor por problemas de estómago o digestivos (tasa de respuesta: 99,36%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>560</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1537</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3457</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2700</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3691</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3421</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5152</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>641</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>686</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>731</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1327</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>731</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3201</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3301</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3428</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3871</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4542</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3895</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3607</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>571</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1591</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>2162</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2930</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2995</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3110</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4654</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2880</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2545</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>577; 5910</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1350</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1351</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4050</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4322</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>1548</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1747</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2037</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1338</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>3584</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>4315</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>445; 4283</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3991</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>556; 5010</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>642; 5413</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4104</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>700; 6422</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>1340; 7752</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>601; 5842</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>1840; 9437</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12B$estomago-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$estomago-Habitat-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por problemas de estómago o digestivos (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por problemas de estómago o digestivos (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -683,12 +683,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,16</t>
+          <t>0,0; 20,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,43</t>
+          <t>0,0; 30,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,85</t>
+          <t>0,0; 51,71</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,51</t>
+          <t>0,0; 14,08</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,22</t>
+          <t>0,0; 32,87</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,47</t>
+          <t>0,0; 28,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -798,17 +798,17 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,28</t>
+          <t>0,0; 15,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,23</t>
+          <t>0,0; 21,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,4</t>
+          <t>0,0; 22,68</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -818,17 +818,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,08</t>
+          <t>0,0; 14,08</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,69</t>
+          <t>0,0; 13,17</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,07</t>
+          <t>0,0; 11,53</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,08</t>
+          <t>0,0; 24,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,83</t>
+          <t>0,0; 25,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -918,27 +918,27 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,17</t>
+          <t>0,0; 15,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,19</t>
+          <t>0,0; 29,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,73</t>
+          <t>0,0; 15,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,24</t>
+          <t>0,0; 12,69</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,1; 21,46</t>
+          <t>2,09; 21,17</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,59</t>
+          <t>0,0; 38,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,92</t>
+          <t>0,0; 24,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,01; 9,76</t>
+          <t>1,02; 9,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,51</t>
+          <t>0,0; 5,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,01; 9,09</t>
+          <t>1,0; 8,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,38; 11,59</t>
+          <t>1,38; 10,38</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,46</t>
+          <t>0,0; 7,1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,46; 13,42</t>
+          <t>1,48; 15,48</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,48; 8,56</t>
+          <t>1,47; 7,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,68</t>
+          <t>0,48; 4,73</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,79; 9,16</t>
+          <t>1,48; 8,64</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por problemas de estómago o digestivos (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por problemas de estómago o digestivos (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2700</t>
+          <t>0; 2669</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 3691</t>
+          <t>0; 3681</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3421</t>
+          <t>0; 3851</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 5152</t>
+          <t>0; 5256</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3201</t>
+          <t>0; 3493</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3301</t>
+          <t>0; 3219</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3428</t>
+          <t>0; 3423</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3871</t>
+          <t>0; 3203</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4542</t>
+          <t>0; 3976</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 3895</t>
+          <t>0; 4388</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 3607</t>
+          <t>0; 4130</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2930</t>
+          <t>0; 3154</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 2995</t>
+          <t>0; 2958</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1763,27 +1763,27 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3110</t>
+          <t>0; 2883</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4654</t>
+          <t>0; 4626</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 2880</t>
+          <t>0; 3309</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 2545</t>
+          <t>0; 3495</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>577; 5910</t>
+          <t>575; 5829</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4050</t>
+          <t>0; 4021</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4322</t>
+          <t>0; 4176</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>445; 4283</t>
+          <t>447; 3956</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 3991</t>
+          <t>0; 3363</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>556; 5010</t>
+          <t>549; 4661</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>642; 5413</t>
+          <t>643; 4849</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 4104</t>
+          <t>0; 4514</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>700; 6422</t>
+          <t>708; 7410</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1340; 7752</t>
+          <t>1329; 7216</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>601; 5842</t>
+          <t>605; 5908</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1840; 9437</t>
+          <t>1520; 8903</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12B$estomago-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$estomago-Habitat-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -630,27 +630,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>13,73%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>3,9%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>6,31%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>13,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -683,12 +683,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,17</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,08</t>
+          <t>0,0; 53,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -698,12 +698,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 16,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,71</t>
+          <t>0,0; 29,86</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,08</t>
+          <t>0,0; 11,27</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,87</t>
+          <t>0,0; 31,76</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4,25%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5,17%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>5,3%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>3,04%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4,25%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>5,17%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,88</t>
+          <t>0,0; 21,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 27,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,88</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,2</t>
+          <t>0,0; 31,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 12,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,08</t>
+          <t>0,0; 14,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,17</t>
+          <t>0,0; 11,47</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,53</t>
+          <t>0,0; 9,54</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3,35%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>9,98%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>7,14%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>4,92%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>3,35%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>9,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,84</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 14,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,51</t>
+          <t>0,0; 33,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 22,45</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,91</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,02</t>
+          <t>0,0; 21,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,78</t>
+          <t>0,0; 15,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,69</t>
+          <t>0,0; 9,37</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,09; 21,17</t>
+          <t>2,09; 21,57</t>
         </is>
       </c>
     </row>
@@ -955,22 +955,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>12,87%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>12,87%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 38,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,31</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,08</t>
+          <t>0,0; 24,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>4,36%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2,1%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5,37%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>3,53%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>1,09%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>3,17%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>4,36%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>2,1%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>5,37%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,02; 9,02</t>
+          <t>1,38; 10,37</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,49</t>
+          <t>0,0; 7,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 8,46</t>
+          <t>1,47; 14,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,38; 10,38</t>
+          <t>1,0; 9,15</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,1</t>
+          <t>0,0; 4,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,48; 15,48</t>
+          <t>1,0; 8,7</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,47; 7,97</t>
+          <t>1,48; 8,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,73</t>
+          <t>0,48; 4,3</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,48; 8,64</t>
+          <t>1,48; 8,91</t>
         </is>
       </c>
     </row>
@@ -1216,14 +1216,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1316,22 +1316,22 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -1369,27 +1369,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>669</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>560</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>977</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1422,12 +1422,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3457</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2669</t>
+          <t>0; 3819</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2825</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 3681</t>
+          <t>0; 2649</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3851</t>
+          <t>0; 3084</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 5256</t>
+          <t>0; 5080</t>
         </is>
       </c>
     </row>
@@ -1479,27 +1479,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1527,32 +1527,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>686</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>731</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>641</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>617</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>686</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>731</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3493</t>
+          <t>0; 3466</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3922</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3219</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3423</t>
+          <t>0; 3755</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 3203</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2544</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3976</t>
+          <t>0; 4172</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 4388</t>
+          <t>0; 3820</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 4130</t>
+          <t>0; 3420</t>
         </is>
       </c>
     </row>
@@ -1637,32 +1637,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1690,32 +1690,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1591</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>907</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>571</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1591</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3154</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2608</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 2958</t>
+          <t>0; 5359</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2851</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 2883</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4626</t>
+          <t>0; 2523</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3309</t>
+          <t>0; 3182</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3495</t>
+          <t>0; 2581</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>575; 5829</t>
+          <t>575; 5938</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1350</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4070</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4021</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4176</t>
+          <t>0; 4172</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1968,22 +1968,22 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>2037</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1338</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2568</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>1548</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>669</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>1747</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>2037</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>1338</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>2568</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>447; 3956</t>
+          <t>643; 4841</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 3363</t>
+          <t>0; 4478</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>549; 4661</t>
+          <t>705; 6971</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>643; 4849</t>
+          <t>440; 4013</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 4514</t>
+          <t>0; 2934</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>708; 7410</t>
+          <t>550; 4798</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1329; 7216</t>
+          <t>1336; 7631</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>605; 5908</t>
+          <t>603; 5364</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1520; 8903</t>
+          <t>1520; 9176</t>
         </is>
       </c>
     </row>
